--- a/tests-dotnet/fixtures/etp-sample/SOR_AGEING_SOR_Ageing.xlsx
+++ b/tests-dotnet/fixtures/etp-sample/SOR_AGEING_SOR_Ageing.xlsx
@@ -559,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,6 +595,18 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>Synthetic CI sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
